--- a/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4710,7 +4710,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>167</v>
       </c>
@@ -4729,7 +4729,7 @@
         <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>74</v>
@@ -5114,7 +5114,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>177</v>
       </c>
@@ -5129,13 +5129,13 @@
         <v>62</v>
       </c>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>74</v>
@@ -5217,7 +5217,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>181</v>
       </c>
@@ -5232,13 +5232,13 @@
         <v>182</v>
       </c>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>74</v>
@@ -5526,7 +5526,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>195</v>
       </c>
@@ -5547,7 +5547,7 @@
         <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>

--- a/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3194" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3194" uniqueCount="343">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -833,6 +833,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Observation.statusCode</t>
@@ -7354,7 +7358,7 @@
         <v>74</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>74</v>
+        <v>267</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>74</v>
@@ -7362,10 +7366,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7391,10 +7395,10 @@
         <v>91</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7425,7 +7429,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>74</v>
@@ -7443,7 +7447,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7463,10 +7467,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7564,10 +7568,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7608,7 +7612,7 @@
         <v>74</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>74</v>
@@ -7667,10 +7671,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7770,10 +7774,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7873,10 +7877,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7976,10 +7980,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8079,10 +8083,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8180,10 +8184,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8281,10 +8285,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8384,10 +8388,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8487,10 +8491,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8590,10 +8594,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8616,13 +8620,13 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8673,7 +8677,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8693,10 +8697,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8719,7 +8723,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8752,7 +8756,7 @@
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>74</v>
@@ -8770,7 +8774,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8790,10 +8794,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8816,7 +8820,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8869,7 +8873,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8889,10 +8893,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8948,25 +8952,25 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF74" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8986,10 +8990,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9012,13 +9016,13 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9069,7 +9073,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9089,10 +9093,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9115,7 +9119,7 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -9148,25 +9152,25 @@
       </c>
       <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF76" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9186,10 +9190,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9212,7 +9216,7 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -9245,25 +9249,25 @@
       </c>
       <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF77" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9283,10 +9287,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9313,7 +9317,7 @@
       </c>
       <c r="L78" s="2"/>
       <c r="M78" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9364,7 +9368,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9384,10 +9388,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9410,7 +9414,7 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -9463,7 +9467,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9483,10 +9487,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9509,7 +9513,7 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
@@ -9562,7 +9566,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9582,10 +9586,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9608,7 +9612,7 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
@@ -9661,7 +9665,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9681,10 +9685,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9707,7 +9711,7 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -9760,7 +9764,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -9780,10 +9784,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9806,7 +9810,7 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
@@ -9859,7 +9863,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -9879,10 +9883,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9905,7 +9909,7 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
@@ -9958,7 +9962,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -9978,10 +9982,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10004,7 +10008,7 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -10057,7 +10061,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10077,10 +10081,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10103,7 +10107,7 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -10156,7 +10160,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10176,10 +10180,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10202,7 +10206,7 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -10255,7 +10259,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10275,10 +10279,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10301,7 +10305,7 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -10354,7 +10358,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10374,10 +10378,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10400,11 +10404,11 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -10455,7 +10459,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10475,10 +10479,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10576,10 +10580,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10677,10 +10681,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10778,10 +10782,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10879,10 +10883,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10982,10 +10986,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11085,10 +11089,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11188,10 +11192,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11291,10 +11295,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11392,10 +11396,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11429,7 +11433,7 @@
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>74</v>
@@ -11451,7 +11455,7 @@
       </c>
       <c r="Y99" s="2"/>
       <c r="Z99" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>74</v>
@@ -11469,7 +11473,7 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -11489,10 +11493,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11515,7 +11519,7 @@
         <v>74</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
@@ -11568,7 +11572,7 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>75</v>
@@ -11588,10 +11592,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11614,7 +11618,7 @@
         <v>74</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
@@ -11667,7 +11671,7 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>

--- a/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-en-rapport-avec-accident-travail.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
